--- a/RouteTimeLoadCalc.xlsx
+++ b/RouteTimeLoadCalc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/williamjames/Documents/08_JPods/03_Technology/route_time/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FA5C82D-83ED-414E-B787-A0DCBBC97A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F54BF0-B3A8-744F-A5EB-A01F3472342A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3260" yWindow="2260" windowWidth="28040" windowHeight="17180" xr2:uid="{A6640582-3751-9B45-BA55-6E8F8A1C2D20}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>seconds to load and leave</t>
   </si>
@@ -62,14 +62,37 @@
     <t>vehicles/hr</t>
   </si>
   <si>
-    <t>people/hr</t>
+    <t>efficacy</t>
+  </si>
+  <si>
+    <t>Cars/day</t>
+  </si>
+  <si>
+    <t>hours/day</t>
+  </si>
+  <si>
+    <t>directions</t>
+  </si>
+  <si>
+    <t>Cars per hou</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -95,14 +118,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -434,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35A5EEF7-0AF2-8B44-AF4A-1EFE4DF38E64}">
-  <dimension ref="D3:E15"/>
+  <dimension ref="B3:E27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="3" spans="4:5" x14ac:dyDescent="0.2">
@@ -496,13 +526,89 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D15">
-        <f>D9*D11</f>
-        <v>624</v>
-      </c>
-      <c r="E15" t="s">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="D17" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="E17" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="D18">
+        <f>D14*D17</f>
+        <v>384</v>
+      </c>
+      <c r="E18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20">
+        <v>8</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B23" s="1">
+        <v>5000</v>
+      </c>
+      <c r="D23" s="3">
+        <f>B23/($D$20*$D$21)</f>
+        <v>312.5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B24" s="1">
+        <v>10000</v>
+      </c>
+      <c r="D24" s="3">
+        <f t="shared" ref="D24:D27" si="0">B24/($D$20*$D$21)</f>
+        <v>625</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B25" s="1">
+        <v>20000</v>
+      </c>
+      <c r="D25" s="3">
+        <f t="shared" si="0"/>
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B26" s="1">
+        <v>30000</v>
+      </c>
+      <c r="D26" s="3">
+        <f t="shared" si="0"/>
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B27" s="1">
+        <v>40000</v>
+      </c>
+      <c r="D27" s="3">
+        <f t="shared" si="0"/>
+        <v>2500</v>
       </c>
     </row>
   </sheetData>
